--- a/engagement_survey_forms/001_organizational_alignment_impact_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/001_organizational_alignment_impact_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Organizational Alignment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>organizational_alignment</t>
+          <t>alignment_mission</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>Alignment to Mission</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,40 +561,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_page_section_2</t>
+          <t>team_objectives_alignment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Team Objectives Alignment</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page_section_3</t>
+          <t>departmental_collaboration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Departmental Collaboration</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_page_section_4</t>
+          <t>leadership_vision</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Leadership Vision</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page_section_5</t>
+          <t>overall_alignment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Overall Alignment</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_page_section_6</t>
+          <t>team_role</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Team Role</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page_section_7</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Adaptability</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_page_section_8</t>
+          <t>collaboration_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Collaboration Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,92 +722,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_page_section_9</t>
+          <t>transparency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Transparency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>first_page_section_10</t>
+          <t>accountability</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Accountability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_page_section_11</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Organizational alignment</t>
+          <t>Page 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>first_page_section_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Organizational alignment</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -822,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,255 +827,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>organizational_alignment_choices</t>
+          <t>alignment_mission_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>organizational_alignment_choices</t>
+          <t>alignment_mission_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>organizational_alignment_choices</t>
+          <t>alignment_mission_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_page_section_3_choices</t>
+          <t>team_objectives_alignment_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_page_section_3_choices</t>
+          <t>team_objectives_alignment_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_page_section_3_choices</t>
+          <t>team_objectives_alignment_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>first_page_section_4_choices</t>
+          <t>leadership_vision_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>very_confident</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Very Confident</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>first_page_section_4_choices</t>
+          <t>leadership_vision_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>somewhat_confident</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Somewhat Confident</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>first_page_section_4_choices</t>
+          <t>leadership_vision_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>first_page_section_7_choices</t>
+          <t>leadership_vision_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>somewhat_uncertain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Somewhat Uncertain</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>first_page_section_7_choices</t>
+          <t>leadership_vision_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>very_uncertain</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Very Uncertain</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>first_page_section_7_choices</t>
+          <t>team_role_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>first_page_section_8_choices</t>
+          <t>team_role_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>somewhat_critical</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>Somewhat Critical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>first_page_section_8_choices</t>
+          <t>team_role_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>first_page_section_8_choices</t>
+          <t>team_role_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>somewhat_unimportant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Somewhat Unimportant</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>team_role_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>not_at_all_important</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Not at all important</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>collaboration_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>very_often</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Very Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>collaboration_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>somewhat_often</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Somewhat Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>collaboration_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>collaboration_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>transparency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>very_open</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Very Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>transparency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>somewhat_open</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Somewhat Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>transparency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>transparency_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>somewhat_closed</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Somewhat Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>transparency_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>very_closed</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Very Closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>accountability_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>very_accountable</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Very Accountable</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>accountability_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>somewhat_accountable</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Somewhat Accountable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>accountability_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>accountability_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>somewhat_unaccountable</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Somewhat Unaccountable</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>accountability_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>not_at_all_accountable</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Not at all Accountable</t>
         </is>
       </c>
     </row>
